--- a/public/modele_etablissements.xlsx
+++ b/public/modele_etablissements.xlsx
@@ -1,35 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aa5cdb37f8cded9e/CAMPS^M/A/Emploi/CNX 4.0/CNX/Clients/SEEG/Elections professionnelles/Modèles importation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP VICTUS AMD RYZEN5\Desktop\CNX 4-0\OHITU\Ohitu\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0269473C-1C49-4EF1-822C-4E144F034086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15F0F79D-CCCC-4EA0-B303-3B71188C5452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8CE91AF2-DDF8-457F-B80C-17332A17A020}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{8CE91AF2-DDF8-457F-B80C-17332A17A020}"/>
   </bookViews>
   <sheets>
     <sheet name="Etablissements" sheetId="1" r:id="rId1"/>
+    <sheet name="Bureaux" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -39,112 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
-  <si>
-    <t>Nzeng-Ayong</t>
-  </si>
-  <si>
-    <t>Etablissement Exploitations Nord</t>
-  </si>
-  <si>
-    <t>EST.</t>
-  </si>
-  <si>
-    <t>La Peyrie</t>
-  </si>
-  <si>
-    <t>Etablissement Peyrie</t>
-  </si>
-  <si>
-    <t>Libreville -Base-Technique</t>
-  </si>
-  <si>
-    <t>Etablissement Base-Technique</t>
-  </si>
-  <si>
-    <t>Libreville -Ancien Siège</t>
-  </si>
-  <si>
-    <t>Etablissement Ancien Siège - Serena Mall</t>
-  </si>
-  <si>
-    <t>Libreville - Siège Social</t>
-  </si>
-  <si>
-    <t>Etablissement Nouveau Siège</t>
-  </si>
-  <si>
-    <t>Centre des métiers Jean Violas - Owendo</t>
-  </si>
-  <si>
-    <t>Etablissement Exploitations Owendo-Damas</t>
-  </si>
-  <si>
-    <t>Ntoum - Siège</t>
-  </si>
-  <si>
-    <t>Etablissement Exploitations Ntoum et Vallée Mbè</t>
-  </si>
-  <si>
-    <t>Moanda - Siège</t>
-  </si>
-  <si>
-    <t>Etablissement Exploitations Moanda et Ogooué-Lolo</t>
-  </si>
-  <si>
-    <t>DRE</t>
-  </si>
-  <si>
-    <t>Franceville - Siège</t>
-  </si>
-  <si>
-    <t>Etablissement Exploitations Franceville et Excentrées</t>
-  </si>
-  <si>
-    <t>Tchibanga - Siège</t>
-  </si>
-  <si>
-    <t>Etablissement Exploitations Nyanga et Excentrées</t>
-  </si>
-  <si>
-    <t>DRCS</t>
-  </si>
-  <si>
-    <t>Mouila - Siège</t>
-  </si>
-  <si>
-    <t>Etablissement Exploitations Ngounié</t>
-  </si>
-  <si>
-    <t>Lambaréné - Siège</t>
-  </si>
-  <si>
-    <t>Etablissement Exploitations Moyen-Ogooué</t>
-  </si>
-  <si>
-    <t>Oyem - Siège</t>
-  </si>
-  <si>
-    <t>Etablissement Exploitations Woleu-Ntem</t>
-  </si>
-  <si>
-    <t>DRN</t>
-  </si>
-  <si>
-    <t>Makokou - Siège</t>
-  </si>
-  <si>
-    <t>Etablissement Exploitations Ogooué-Ivindo</t>
-  </si>
-  <si>
-    <t>Port-Gentil - Siège</t>
-  </si>
-  <si>
-    <t>Etablissement Exploitations Littoral</t>
-  </si>
-  <si>
-    <t>DRL</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>Nbre _electeurs_Execution</t>
   </si>
@@ -179,17 +64,20 @@
     <t>Responsable_Etablissement</t>
   </si>
   <si>
-    <t>Nom_Etablissement__Site</t>
-  </si>
-  <si>
     <t>Region__Localisation</t>
+  </si>
+  <si>
+    <t>Bureau</t>
+  </si>
+  <si>
+    <t>Nom_Etablissement__Centre</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -202,6 +90,16 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -238,16 +136,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{FB530DCB-02C4-42DF-9BB7-CEE2470CD924}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{FC0DEB12-771D-484E-94FE-0C74ABB18B88}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -587,10 +489,10 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.59765625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44.5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -600,327 +502,77 @@
     <col min="8" max="8" width="17.5" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.8984375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="27.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="11.19921875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="1" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D657B3-AF51-49CE-90EB-25EB91A847E9}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="44.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="11.19921875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="1">
-        <v>2</v>
-      </c>
-      <c r="H12" s="1">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>1</v>
-      </c>
-      <c r="I14" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1</v>
-      </c>
-      <c r="I15" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
